--- a/tests/TC-16/results/timetable_all_departments_even.xlsx
+++ b/tests/TC-16/results/timetable_all_departments_even.xlsx
@@ -107,7 +107,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="6">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -137,13 +137,6 @@
     </border>
     <border>
       <left/>
-      <right/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
@@ -153,7 +146,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -184,7 +177,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -810,16 +802,9 @@
         </is>
       </c>
       <c r="M2" s="8" t="inlineStr"/>
-      <c r="N2" s="10" t="inlineStr">
-        <is>
-          <t>CS401
-LEC
-Room: 101
-Dr. A</t>
-        </is>
-      </c>
-      <c r="O2" s="11" t="n"/>
-      <c r="P2" s="12" t="n"/>
+      <c r="N2" s="8" t="inlineStr"/>
+      <c r="O2" s="8" t="inlineStr"/>
+      <c r="P2" s="8" t="inlineStr"/>
       <c r="Q2" s="8" t="inlineStr"/>
       <c r="R2" s="8" t="inlineStr"/>
       <c r="S2" s="8" t="inlineStr"/>
@@ -841,11 +826,7 @@
           <t>Minor Slot</t>
         </is>
       </c>
-      <c r="C3" s="8" t="inlineStr"/>
-      <c r="D3" s="8" t="inlineStr"/>
-      <c r="E3" s="8" t="inlineStr"/>
-      <c r="F3" s="8" t="inlineStr"/>
-      <c r="G3" s="10" t="inlineStr">
+      <c r="C3" s="10" t="inlineStr">
         <is>
           <t>CS401
 LEC
@@ -853,9 +834,13 @@
 Dr. A</t>
         </is>
       </c>
-      <c r="H3" s="11" t="n"/>
-      <c r="I3" s="11" t="n"/>
-      <c r="J3" s="12" t="n"/>
+      <c r="D3" s="11" t="n"/>
+      <c r="E3" s="8" t="inlineStr"/>
+      <c r="F3" s="8" t="inlineStr"/>
+      <c r="G3" s="8" t="inlineStr"/>
+      <c r="H3" s="8" t="inlineStr"/>
+      <c r="I3" s="8" t="inlineStr"/>
+      <c r="J3" s="8" t="inlineStr"/>
       <c r="K3" s="8" t="inlineStr"/>
       <c r="L3" s="9" t="inlineStr">
         <is>
@@ -887,8 +872,15 @@
           <t>Minor Slot</t>
         </is>
       </c>
-      <c r="C4" s="8" t="inlineStr"/>
-      <c r="D4" s="8" t="inlineStr"/>
+      <c r="C4" s="10" t="inlineStr">
+        <is>
+          <t>CS401
+LEC
+Room: 101
+Dr. A</t>
+        </is>
+      </c>
+      <c r="D4" s="11" t="n"/>
       <c r="E4" s="8" t="inlineStr"/>
       <c r="F4" s="8" t="inlineStr"/>
       <c r="G4" s="8" t="inlineStr"/>
@@ -931,16 +923,9 @@
       <c r="E5" s="8" t="inlineStr"/>
       <c r="F5" s="8" t="inlineStr"/>
       <c r="G5" s="8" t="inlineStr"/>
-      <c r="H5" s="10" t="inlineStr">
-        <is>
-          <t>CS401
-TUT
-Room: 101
-Dr. A</t>
-        </is>
-      </c>
-      <c r="I5" s="11" t="n"/>
-      <c r="J5" s="12" t="n"/>
+      <c r="H5" s="8" t="inlineStr"/>
+      <c r="I5" s="8" t="inlineStr"/>
+      <c r="J5" s="8" t="inlineStr"/>
       <c r="K5" s="8" t="inlineStr"/>
       <c r="L5" s="9" t="inlineStr">
         <is>
@@ -993,7 +978,14 @@
       <c r="Q6" s="8" t="inlineStr"/>
       <c r="R6" s="8" t="inlineStr"/>
       <c r="S6" s="8" t="inlineStr"/>
-      <c r="T6" s="8" t="inlineStr"/>
+      <c r="T6" s="10" t="inlineStr">
+        <is>
+          <t>CS401
+TUT
+Room: 101
+Dr. A</t>
+        </is>
+      </c>
       <c r="U6" s="7" t="inlineStr">
         <is>
           <t>Minor Slot</t>
@@ -1001,77 +993,76 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="13" t="inlineStr">
+      <c r="A9" s="12" t="inlineStr">
         <is>
           <t>Course Details</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="14" t="inlineStr">
+      <c r="A11" s="13" t="inlineStr">
         <is>
           <t>Course Code</t>
         </is>
       </c>
-      <c r="B11" s="14" t="inlineStr">
+      <c r="B11" s="13" t="inlineStr">
         <is>
           <t>Color</t>
         </is>
       </c>
-      <c r="C11" s="14" t="inlineStr">
+      <c r="C11" s="13" t="inlineStr">
         <is>
           <t>Name of the Course</t>
         </is>
       </c>
-      <c r="D11" s="14" t="inlineStr">
+      <c r="D11" s="13" t="inlineStr">
         <is>
           <t>Course Co-ordinator</t>
         </is>
       </c>
-      <c r="E11" s="14" t="inlineStr">
+      <c r="E11" s="13" t="inlineStr">
         <is>
           <t>LTPSC</t>
         </is>
       </c>
-      <c r="F11" s="14" t="inlineStr">
+      <c r="F11" s="13" t="inlineStr">
         <is>
           <t>Room Number</t>
         </is>
       </c>
     </row>
     <row r="12" ht="30" customHeight="1">
-      <c r="A12" s="15" t="inlineStr">
+      <c r="A12" s="14" t="inlineStr">
         <is>
           <t>CS401</t>
         </is>
       </c>
-      <c r="B12" s="16" t="inlineStr"/>
-      <c r="C12" s="15" t="inlineStr">
+      <c r="B12" s="15" t="inlineStr"/>
+      <c r="C12" s="14" t="inlineStr">
         <is>
           <t>Scheduled Course</t>
         </is>
       </c>
-      <c r="D12" s="15" t="inlineStr">
+      <c r="D12" s="14" t="inlineStr">
         <is>
           <t>Dr. A</t>
         </is>
       </c>
-      <c r="E12" s="15" t="inlineStr">
+      <c r="E12" s="14" t="inlineStr">
         <is>
           <t>3-1-0-0-4</t>
         </is>
       </c>
-      <c r="F12" s="15" t="inlineStr">
+      <c r="F12" s="14" t="inlineStr">
         <is>
           <t>101</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="3">
-    <mergeCell ref="H5:J5"/>
-    <mergeCell ref="N2:P2"/>
-    <mergeCell ref="G3:J3"/>
+  <mergeCells count="2">
+    <mergeCell ref="C3:D3"/>
+    <mergeCell ref="C4:D4"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1243,16 +1234,9 @@
         </is>
       </c>
       <c r="M2" s="8" t="inlineStr"/>
-      <c r="N2" s="10" t="inlineStr">
-        <is>
-          <t>CS401
-LEC
-Room: 101
-Dr. A</t>
-        </is>
-      </c>
-      <c r="O2" s="11" t="n"/>
-      <c r="P2" s="12" t="n"/>
+      <c r="N2" s="8" t="inlineStr"/>
+      <c r="O2" s="8" t="inlineStr"/>
+      <c r="P2" s="8" t="inlineStr"/>
       <c r="Q2" s="8" t="inlineStr"/>
       <c r="R2" s="8" t="inlineStr"/>
       <c r="S2" s="8" t="inlineStr"/>
@@ -1274,11 +1258,7 @@
           <t>Minor Slot</t>
         </is>
       </c>
-      <c r="C3" s="8" t="inlineStr"/>
-      <c r="D3" s="8" t="inlineStr"/>
-      <c r="E3" s="8" t="inlineStr"/>
-      <c r="F3" s="8" t="inlineStr"/>
-      <c r="G3" s="10" t="inlineStr">
+      <c r="C3" s="10" t="inlineStr">
         <is>
           <t>CS401
 LEC
@@ -1286,9 +1266,13 @@
 Dr. A</t>
         </is>
       </c>
-      <c r="H3" s="11" t="n"/>
-      <c r="I3" s="11" t="n"/>
-      <c r="J3" s="12" t="n"/>
+      <c r="D3" s="11" t="n"/>
+      <c r="E3" s="8" t="inlineStr"/>
+      <c r="F3" s="8" t="inlineStr"/>
+      <c r="G3" s="8" t="inlineStr"/>
+      <c r="H3" s="8" t="inlineStr"/>
+      <c r="I3" s="8" t="inlineStr"/>
+      <c r="J3" s="8" t="inlineStr"/>
       <c r="K3" s="8" t="inlineStr"/>
       <c r="L3" s="9" t="inlineStr">
         <is>
@@ -1320,8 +1304,15 @@
           <t>Minor Slot</t>
         </is>
       </c>
-      <c r="C4" s="8" t="inlineStr"/>
-      <c r="D4" s="8" t="inlineStr"/>
+      <c r="C4" s="10" t="inlineStr">
+        <is>
+          <t>CS401
+LEC
+Room: 101
+Dr. A</t>
+        </is>
+      </c>
+      <c r="D4" s="11" t="n"/>
       <c r="E4" s="8" t="inlineStr"/>
       <c r="F4" s="8" t="inlineStr"/>
       <c r="G4" s="8" t="inlineStr"/>
@@ -1364,16 +1355,9 @@
       <c r="E5" s="8" t="inlineStr"/>
       <c r="F5" s="8" t="inlineStr"/>
       <c r="G5" s="8" t="inlineStr"/>
-      <c r="H5" s="10" t="inlineStr">
-        <is>
-          <t>CS401
-TUT
-Room: 101
-Dr. A</t>
-        </is>
-      </c>
-      <c r="I5" s="11" t="n"/>
-      <c r="J5" s="12" t="n"/>
+      <c r="H5" s="8" t="inlineStr"/>
+      <c r="I5" s="8" t="inlineStr"/>
+      <c r="J5" s="8" t="inlineStr"/>
       <c r="K5" s="8" t="inlineStr"/>
       <c r="L5" s="9" t="inlineStr">
         <is>
@@ -1426,7 +1410,14 @@
       <c r="Q6" s="8" t="inlineStr"/>
       <c r="R6" s="8" t="inlineStr"/>
       <c r="S6" s="8" t="inlineStr"/>
-      <c r="T6" s="8" t="inlineStr"/>
+      <c r="T6" s="10" t="inlineStr">
+        <is>
+          <t>CS401
+TUT
+Room: 101
+Dr. A</t>
+        </is>
+      </c>
       <c r="U6" s="7" t="inlineStr">
         <is>
           <t>Minor Slot</t>
@@ -1434,77 +1425,76 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="13" t="inlineStr">
+      <c r="A9" s="12" t="inlineStr">
         <is>
           <t>Course Details</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="14" t="inlineStr">
+      <c r="A11" s="13" t="inlineStr">
         <is>
           <t>Course Code</t>
         </is>
       </c>
-      <c r="B11" s="14" t="inlineStr">
+      <c r="B11" s="13" t="inlineStr">
         <is>
           <t>Color</t>
         </is>
       </c>
-      <c r="C11" s="14" t="inlineStr">
+      <c r="C11" s="13" t="inlineStr">
         <is>
           <t>Name of the Course</t>
         </is>
       </c>
-      <c r="D11" s="14" t="inlineStr">
+      <c r="D11" s="13" t="inlineStr">
         <is>
           <t>Course Co-ordinator</t>
         </is>
       </c>
-      <c r="E11" s="14" t="inlineStr">
+      <c r="E11" s="13" t="inlineStr">
         <is>
           <t>LTPSC</t>
         </is>
       </c>
-      <c r="F11" s="14" t="inlineStr">
+      <c r="F11" s="13" t="inlineStr">
         <is>
           <t>Room Number</t>
         </is>
       </c>
     </row>
     <row r="12" ht="30" customHeight="1">
-      <c r="A12" s="15" t="inlineStr">
+      <c r="A12" s="14" t="inlineStr">
         <is>
           <t>CS401</t>
         </is>
       </c>
-      <c r="B12" s="16" t="inlineStr"/>
-      <c r="C12" s="15" t="inlineStr">
+      <c r="B12" s="15" t="inlineStr"/>
+      <c r="C12" s="14" t="inlineStr">
         <is>
           <t>Scheduled Course</t>
         </is>
       </c>
-      <c r="D12" s="15" t="inlineStr">
+      <c r="D12" s="14" t="inlineStr">
         <is>
           <t>Dr. A</t>
         </is>
       </c>
-      <c r="E12" s="15" t="inlineStr">
+      <c r="E12" s="14" t="inlineStr">
         <is>
           <t>3-1-0-0-4</t>
         </is>
       </c>
-      <c r="F12" s="15" t="inlineStr">
+      <c r="F12" s="14" t="inlineStr">
         <is>
           <t>101</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="3">
-    <mergeCell ref="H5:J5"/>
-    <mergeCell ref="N2:P2"/>
-    <mergeCell ref="G3:J3"/>
+  <mergeCells count="2">
+    <mergeCell ref="C3:D3"/>
+    <mergeCell ref="C4:D4"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1516,7 +1506,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H7"/>
+  <dimension ref="A1:H5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1568,13 +1558,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C2" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -1604,13 +1594,13 @@
         </is>
       </c>
       <c r="B3" t="n">
+        <v>4</v>
+      </c>
+      <c r="C3" t="n">
         <v>3</v>
       </c>
-      <c r="C3" t="n">
-        <v>7</v>
-      </c>
       <c r="D3" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -1636,17 +1626,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>CSE_4_A</t>
+          <t>CSE_4_B</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="D4" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -1660,7 +1650,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>TUT</t>
+          <t>LEC</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -1676,13 +1666,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="D5" t="n">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -1700,78 +1690,6 @@
         </is>
       </c>
       <c r="H5" t="inlineStr">
-        <is>
-          <t>CS401</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>CSE_4_B</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>3</v>
-      </c>
-      <c r="C6" t="n">
-        <v>7</v>
-      </c>
-      <c r="D6" t="n">
-        <v>10</v>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>Dr. A</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>101</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>LEC</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>CS401</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>CSE_4_B</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>5</v>
-      </c>
-      <c r="C7" t="n">
-        <v>8</v>
-      </c>
-      <c r="D7" t="n">
-        <v>10</v>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>Dr. A</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>101</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>TUT</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
         <is>
           <t>CS401</t>
         </is>
